--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ87"/>
+  <dimension ref="A1:AQ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12429,10 +12429,8 @@
           <t>2025,2015,2035,2135,2125</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="Y83" t="n">
+        <v>-5</v>
       </c>
       <c r="Z83" t="n">
         <v>-1952000</v>
@@ -12574,10 +12572,8 @@
           <t>12750,12990,13010,13340,13160</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y84" t="n">
+        <v>6</v>
       </c>
       <c r="Z84" t="n">
         <v>6000</v>
@@ -12719,10 +12715,8 @@
           <t>1647000,1783000,1793000,1856000,1853000</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y85" t="n">
+        <v>4</v>
       </c>
       <c r="Z85" t="n">
         <v>-393000</v>
@@ -12864,10 +12858,8 @@
           <t>16850,18410,19970,19450,19750</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y86" t="n">
+        <v>1</v>
       </c>
       <c r="Z86" t="n">
         <v>28000</v>
@@ -13013,10 +13005,8 @@
           <t>10820,11230,11990,12090,14510</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y87" t="n">
+        <v>7</v>
       </c>
       <c r="Z87" t="n">
         <v>-339000</v>
@@ -13068,6 +13058,739 @@
       <c r="AQ87" t="inlineStr">
         <is>
           <t>중동 전쟁 및 국제 유가 급등에 따른 전쟁 테마주로 급등. WTI 100달러 돌파 및 3연상 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:01</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>017900</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>40</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="L88" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="n">
+        <v>9740</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>+23.29%</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>25399779</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>236221680415</v>
+      </c>
+      <c r="R88" t="n">
+        <v>104.57</v>
+      </c>
+      <c r="S88" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="T88" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="U88" t="n">
+        <v>113</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" t="n">
+        <v>5.431122724426113</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>7090,8180,8220,8050,7900</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="n">
+        <v>133.42</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>4784</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>22450</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>1760</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>5644</v>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>차세대 광반도체 및 광통신 테마 부각. 급락장 속에서도 긍정적 흐름 유지 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:01</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>40</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="L89" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="n">
+        <v>14500</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>+2.47%</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>6759732</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>97011429315</v>
+      </c>
+      <c r="R89" t="n">
+        <v>109.93</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T89" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="U89" t="n">
+        <v>111</v>
+      </c>
+      <c r="V89" t="n">
+        <v>14</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1.596386308690673</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>13470,13700,14960,14740,14150</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z89" t="n">
+        <v>-430000</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="n">
+        <v>-59.92</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>22545</v>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>AI 관련 AIDC 광통신 기술 성장 수혜 기대. GPU 확보 뉴스와 함께 기술력 부각.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:01</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>엑스게이트</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>356680</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>40</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="L90" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="n">
+        <v>16990</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>+5.79%</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>14021184</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>246587302330</v>
+      </c>
+      <c r="R90" t="n">
+        <v>81.45999999999999</v>
+      </c>
+      <c r="S90" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U90" t="n">
+        <v>114</v>
+      </c>
+      <c r="V90" t="n">
+        <v>2</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0.1182432432432432</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>11330,11600,12610,12360,16060</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z90" t="n">
+        <v>-292000</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="n">
+        <v>121.36</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1557</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>30550</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>6100</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>4850</v>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>AI 개발 속도 조절론으로 인한 등락 속에 지지선 이탈 및 반등 시도 관측.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:01</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>40</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="L91" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="n">
+        <v>14650</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>+0.27%</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>6395527</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>99176198490</v>
+      </c>
+      <c r="R91" t="n">
+        <v>76.34999999999999</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T91" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="U91" t="n">
+        <v>248</v>
+      </c>
+      <c r="V91" t="n">
+        <v>4</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0.5287853063744405</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>11230,11990,12090,14510,14610</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z91" t="n">
+        <v>-128000</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="n">
+        <v>357.32</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>41</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>5307</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>36200</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>8920</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>2198</v>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>이란-걸프국가 회담 연기 및 호르무즈 해협 긴장 고조로 국제 유가 폭등. 저가 매수 기회 포착.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:01</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>5</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>페니트리움바이오</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>187660</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>40</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="L92" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="n">
+        <v>8250</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>2448292</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>20835519010</v>
+      </c>
+      <c r="R92" t="n">
+        <v>84.22</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T92" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="U92" t="n">
+        <v>137</v>
+      </c>
+      <c r="V92" t="n">
+        <v>6</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0.9316653960773442</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>6470,5710,7420,8300,8290</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>64000</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>-118.31</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>330.36</v>
+      </c>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="n">
+        <v>-18.92</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>-436</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>152</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>21500</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>2300</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>5277</v>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>항암 신약 관련 글로벌 심포지엄 개최 및 임상 결과에 대한 기대감으로 인한 목표가 상향 전망.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ92"/>
+  <dimension ref="A1:AQ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13148,10 +13148,8 @@
           <t>7090,8180,8220,8050,7900</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y88" t="n">
+        <v>6</v>
       </c>
       <c r="Z88" t="n">
         <v>1000</v>
@@ -13293,10 +13291,8 @@
           <t>13470,13700,14960,14740,14150</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y89" t="n">
+        <v>5</v>
       </c>
       <c r="Z89" t="n">
         <v>-430000</v>
@@ -13442,10 +13438,8 @@
           <t>11330,11600,12610,12360,16060</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y90" t="n">
+        <v>1</v>
       </c>
       <c r="Z90" t="n">
         <v>-292000</v>
@@ -13591,10 +13585,8 @@
           <t>11230,11990,12090,14510,14610</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y91" t="n">
+        <v>3</v>
       </c>
       <c r="Z91" t="n">
         <v>-128000</v>
@@ -13736,10 +13728,8 @@
           <t>6470,5710,7420,8300,8290</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y92" t="n">
+        <v>6</v>
       </c>
       <c r="Z92" t="n">
         <v>64000</v>
@@ -13791,6 +13781,747 @@
       <c r="AQ92" t="inlineStr">
         <is>
           <t>항암 신약 관련 글로벌 심포지엄 개최 및 임상 결과에 대한 기대감으로 인한 목표가 상향 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:01</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>30</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="L93" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="n">
+        <v>22100</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>+3.27%</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>4099000</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>89734232850</v>
+      </c>
+      <c r="R93" t="n">
+        <v>229.42</v>
+      </c>
+      <c r="S93" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="T93" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U93" t="n">
+        <v>140</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1</v>
+      </c>
+      <c r="W93" t="n">
+        <v>3.905082812481814</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>21400,21300,21600,21350,21400</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z93" t="n">
+        <v>688000</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>49000</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>281.28</v>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE93" t="n">
+        <v>32000</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>-31.56</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>620</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>4857</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>35350</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>18440</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>194480</v>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>대형 수주 공시 확인 및 숏커버, 목표주가 상향 등 긍정적 뉴스 기반 분석.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>30</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="L94" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>4310</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>+11.37%</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>71162060</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>304902210546</v>
+      </c>
+      <c r="R94" t="n">
+        <v>100.71</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="T94" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="U94" t="n">
+        <v>202</v>
+      </c>
+      <c r="V94" t="n">
+        <v>5</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1.505243985190653</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>2800,3640,3810,3925,3870</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z94" t="n">
+        <v>-202000</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>-17.45</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>947</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>8100</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>592</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>4857</v>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>6G 시대 개막 및 국책사업 선정 가능성에 따른 기대감 표출.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:01</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>30</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="L95" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>249000</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>-4.05%</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>14699486</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>3686047066750</v>
+      </c>
+      <c r="R95" t="n">
+        <v>80.51000000000001</v>
+      </c>
+      <c r="S95" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="T95" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="U95" t="n">
+        <v>800</v>
+      </c>
+      <c r="V95" t="n">
+        <v>105</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0.240233967696582</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>270000,269500,269500,269000,259500</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z95" t="n">
+        <v>-2979000</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>-1253000</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE95" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>-37.25</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>75900</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>14557234</v>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>AI 속도 조절론 관련 언급. 정치적 이슈와 함께 주가 부진에 대한 불만 표출.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:01</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>30</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="L96" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>86800</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>-4.41%</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>2594751</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>228582182650</v>
+      </c>
+      <c r="R96" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="S96" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="T96" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="U96" t="n">
+        <v>263</v>
+      </c>
+      <c r="V96" t="n">
+        <v>14</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0.5860381823414665</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>87900,89500,91700,89900,90800</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z96" t="n">
+        <v>-621000</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>-125000</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="n">
+        <v>657.58</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>556007</v>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>국제 유가 상승 및 원전 관련 긍정적 전망. 금리 인상 분위기 및 프로그램 매도에 대한 우려.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:01</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>30</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="L97" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="n">
+        <v>1693000</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>-6.57%</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>3257246</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>5582528941000</v>
+      </c>
+      <c r="R97" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="S97" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="T97" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U97" t="n">
+        <v>800</v>
+      </c>
+      <c r="V97" t="n">
+        <v>70</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0.3139230139230139</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>1783000,1793000,1856000,1853000,1812000</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z97" t="n">
+        <v>-1117000</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>-203000</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE97" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>-25.35</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>325000</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>12367236</v>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>AI 개발 속도 조절론 및 국내 정치 상황 언급. 반도체 섹터 전반의 하락 추세 및 불안감.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ97"/>
+  <dimension ref="A1:AQ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13871,10 +13871,8 @@
           <t>21400,21300,21600,21350,21400</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y93" t="n">
+        <v>3</v>
       </c>
       <c r="Z93" t="n">
         <v>688000</v>
@@ -14020,10 +14018,8 @@
           <t>2800,3640,3810,3925,3870</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y94" t="n">
+        <v>4</v>
       </c>
       <c r="Z94" t="n">
         <v>-202000</v>
@@ -14165,10 +14161,8 @@
           <t>270000,269500,269500,269000,259500</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
+      <c r="Y95" t="n">
+        <v>-5</v>
       </c>
       <c r="Z95" t="n">
         <v>-2979000</v>
@@ -14314,10 +14308,8 @@
           <t>87900,89500,91700,89900,90800</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y96" t="n">
+        <v>-3</v>
       </c>
       <c r="Z96" t="n">
         <v>-621000</v>
@@ -14463,10 +14455,8 @@
           <t>1783000,1793000,1856000,1853000,1812000</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y97" t="n">
+        <v>-8</v>
       </c>
       <c r="Z97" t="n">
         <v>-1117000</v>
@@ -14522,6 +14512,751 @@
       <c r="AQ97" t="inlineStr">
         <is>
           <t>AI 개발 속도 조절론 및 국내 정치 상황 언급. 반도체 섹터 전반의 하락 추세 및 불안감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>336260</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>35</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L98" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="n">
+        <v>51100</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>+6.90%</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>1439944</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>74420965275</v>
+      </c>
+      <c r="R98" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="S98" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="T98" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="U98" t="n">
+        <v>130</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0.7893995647164256</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>49250,53900,50100,48800,46400</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z98" t="n">
+        <v>89000</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>21000</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>-48.11</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE98" t="n">
+        <v>74000</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>-28.51</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="n">
+        <v>-31.48</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>-1623</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>4491</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>108900</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>18230</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>33467</v>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>5천억 수주 공시 후 주가 급등. 미국 진출 본격화 및 수소법 시행 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:01</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>35</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L99" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
+        <v>31800</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>+4.78%</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>347832</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>10926243650</v>
+      </c>
+      <c r="R99" t="n">
+        <v>144.57</v>
+      </c>
+      <c r="S99" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="T99" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U99" t="n">
+        <v>139</v>
+      </c>
+      <c r="V99" t="n">
+        <v>1</v>
+      </c>
+      <c r="W99" t="n">
+        <v>1.199816007359706</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>31650,31500,31650,31450,30250</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z99" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="n">
+        <v>-18.96</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>42357</v>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>HLB, FDA 승인 기대감 속 담관암 신약 관련 소식 혼재. 기관 외인 동향 주시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>삼익제약</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>014950</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>35</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L100" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
+        <v>10770</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>+16.18%</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>12110474</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>133228096275</v>
+      </c>
+      <c r="R100" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T100" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U100" t="n">
+        <v>88</v>
+      </c>
+      <c r="V100" t="n">
+        <v>2</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0.3719208928921089</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>8750,9010,8300,7910,9480</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z100" t="n">
+        <v>16000</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="n">
+        <v>-131.34</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>-82</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>7503</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>25050</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>3705</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>1084</v>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>면역조절 펩타이드 신기술 특허 등록. 장기지속형 제제 기술 기반 상승 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:01</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" t="n">
+        <v>35</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L101" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="n">
+        <v>1724000</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>+1.59%</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>1385366</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>2366805191500</v>
+      </c>
+      <c r="R101" t="n">
+        <v>127.86</v>
+      </c>
+      <c r="S101" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="T101" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U101" t="n">
+        <v>800</v>
+      </c>
+      <c r="V101" t="n">
+        <v>71</v>
+      </c>
+      <c r="W101" t="n">
+        <v>7.342316258351893</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>1793000,1856000,1853000,1812000,1683000</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z101" t="n">
+        <v>-118000</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>-48000</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE101" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>-25.83</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>325000</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>12593688</v>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>나스닥 선물 및 코스피 야간 선물 흐름 긍정적. 외인 매도세 속 기관 매수세 유입.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:01</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>35</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L102" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="n">
+        <v>251500</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>+1.00%</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>5060339</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1265343172500</v>
+      </c>
+      <c r="R102" t="n">
+        <v>105.64</v>
+      </c>
+      <c r="S102" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="T102" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="U102" t="n">
+        <v>800</v>
+      </c>
+      <c r="V102" t="n">
+        <v>106</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0.7481904781895337</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>269500,269500,269000,259500,248500</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z102" t="n">
+        <v>-176000</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>-267000</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE102" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>-37.88</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>75900</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>14703391</v>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>시장 안정화 및 메모리 반도체 수요 유지 기대감. 악재 선반영 후 급반등 전망.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ102"/>
+  <dimension ref="A1:AQ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14602,10 +14602,8 @@
           <t>49250,53900,50100,48800,46400</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y98" t="n">
+        <v>3</v>
       </c>
       <c r="Z98" t="n">
         <v>89000</v>
@@ -14751,10 +14749,8 @@
           <t>31650,31500,31650,31450,30250</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y99" t="n">
+        <v>3</v>
       </c>
       <c r="Z99" t="n">
         <v>25000</v>
@@ -14900,10 +14896,8 @@
           <t>8750,9010,8300,7910,9480</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y100" t="n">
+        <v>5</v>
       </c>
       <c r="Z100" t="n">
         <v>16000</v>
@@ -15049,10 +15043,8 @@
           <t>1793000,1856000,1853000,1812000,1683000</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y101" t="n">
+        <v>2</v>
       </c>
       <c r="Z101" t="n">
         <v>-118000</v>
@@ -15198,10 +15190,8 @@
           <t>269500,269500,269000,259500,248500</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y102" t="n">
+        <v>1</v>
       </c>
       <c r="Z102" t="n">
         <v>-176000</v>
@@ -15257,6 +15247,743 @@
       <c r="AQ102" t="inlineStr">
         <is>
           <t>시장 안정화 및 메모리 반도체 수요 유지 기대감. 악재 선반영 후 급반등 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:01</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>한국첨단소재</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>062970</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>25</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="L103" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="n">
+        <v>3360</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>+29.98%</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>41109019</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>125621270000</v>
+      </c>
+      <c r="R103" t="n">
+        <v>89.81999999999999</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U103" t="n">
+        <v>145</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>2020,1930,1904,1990,2585</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z103" t="n">
+        <v>-389000</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>68.09</v>
+      </c>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>-952</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>276</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>5100</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>966</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>1012</v>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>삼성과 4381억 규모 계약 체결, 광통신 및 양자 관련 테마주로 급등 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>096770</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1</v>
+      </c>
+      <c r="J104" t="n">
+        <v>25</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="L104" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="n">
+        <v>142100</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>+3.95%</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>874399</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>124017876350</v>
+      </c>
+      <c r="R104" t="n">
+        <v>116.53</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U104" t="n">
+        <v>145</v>
+      </c>
+      <c r="V104" t="n">
+        <v>1</v>
+      </c>
+      <c r="W104" t="n">
+        <v>2.894501278772379</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>138000,153500,153100,144800,133900</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z104" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE104" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>-21056</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>129848</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>164700</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>87700</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>240224</v>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>합병 반대 의견 및 정유/배터리 업황 슈퍼 사이클 기대. 주가 변동성에 대한 우려.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:01</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>3</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>158430</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>25</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="L105" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>6310</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>+29.84%</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>11524846</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>65940988385</v>
+      </c>
+      <c r="R105" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="S105" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T105" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="U105" t="n">
+        <v>120</v>
+      </c>
+      <c r="V105" t="n">
+        <v>1</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>4560,4665,4630,4825,4900</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z105" t="n">
+        <v>-439000</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>60.18</v>
+      </c>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="n">
+        <v>100.16</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>63</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>4240</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>11370</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>3300</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>1545</v>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>양자 보안 테마 강세. 클래리티 법안 통과 여부가 주가에 영향을 줄 것으로 예상. 10000원 돌파 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>042700</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="n">
+        <v>25</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="L106" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>222000</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>-1.33%</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>448461</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>100471095500</v>
+      </c>
+      <c r="R106" t="n">
+        <v>104.37</v>
+      </c>
+      <c r="S106" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U106" t="n">
+        <v>182</v>
+      </c>
+      <c r="V106" t="n">
+        <v>2</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0.2441211052322163</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>244500,250500,253000,231000,226000</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z106" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE106" t="n">
+        <v>380000</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>-40.92</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>2233</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>7278</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>426000</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>89500</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>211593</v>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>머스크 테슬라향 패키징 장비 공급 뉴스 기반 급등 조짐. 공매도 관련 언급 다수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:01</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>5</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>25</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="L107" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>86200</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>1861019</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>159510557700</v>
+      </c>
+      <c r="R107" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="S107" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="T107" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U107" t="n">
+        <v>290</v>
+      </c>
+      <c r="V107" t="n">
+        <v>15</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1.223009095327362</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>89500,91700,89900,90800,85600</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z107" t="n">
+        <v>-220000</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>-152000</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE107" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>-28.92</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="n">
+        <v>653.03</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>552164</v>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>원전 관련 ETF 추가 출시 및 긍정적인 시나리오가 제시되는 가운데, 엑스에너지의 급등이 두산에너빌리티의 상승 기대감을 높임. 유가 상승에 따른 에너지 독립 필요성이 부각됨.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ107"/>
+  <dimension ref="A1:AQ112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15337,10 +15337,8 @@
           <t>2020,1930,1904,1990,2585</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y103" t="n">
+        <v>6</v>
       </c>
       <c r="Z103" t="n">
         <v>-389000</v>
@@ -15482,10 +15480,8 @@
           <t>138000,153500,153100,144800,133900</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y104" t="n">
+        <v>1</v>
       </c>
       <c r="Z104" t="n">
         <v>-3000</v>
@@ -15631,10 +15627,8 @@
           <t>4560,4665,4630,4825,4900</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y105" t="n">
+        <v>7</v>
       </c>
       <c r="Z105" t="n">
         <v>-439000</v>
@@ -15776,10 +15770,8 @@
           <t>244500,250500,253000,231000,226000</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y106" t="n">
+        <v>2</v>
       </c>
       <c r="Z106" t="n">
         <v>-120000</v>
@@ -15925,10 +15917,8 @@
           <t>89500,91700,89900,90800,85600</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y107" t="n">
+        <v>3</v>
       </c>
       <c r="Z107" t="n">
         <v>-220000</v>
@@ -15984,6 +15974,739 @@
       <c r="AQ107" t="inlineStr">
         <is>
           <t>원전 관련 ETF 추가 출시 및 긍정적인 시나리오가 제시되는 가운데, 엑스에너지의 급등이 두산에너빌리티의 상승 기대감을 높임. 유가 상승에 따른 에너지 독립 필요성이 부각됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:01</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>004310</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>30</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="L108" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="n">
+        <v>10520</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>+3.95%</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>9788346</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>101785644010</v>
+      </c>
+      <c r="R108" t="n">
+        <v>101.21</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U108" t="n">
+        <v>101</v>
+      </c>
+      <c r="V108" t="n">
+        <v>2</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0.2623284100781929</v>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>10300,9770,9820,10030,10070</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z108" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>15960</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>3366</v>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>미프진 도입 공식화 관련 재료 소멸 및 주가 하락 우려, 단기 반등 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:01</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" t="n">
+        <v>30</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="L109" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="n">
+        <v>4530</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>+9.95%</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>62702085</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>287577517279</v>
+      </c>
+      <c r="R109" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="T109" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="U109" t="n">
+        <v>120</v>
+      </c>
+      <c r="V109" t="n">
+        <v>7</v>
+      </c>
+      <c r="W109" t="n">
+        <v>2.44953811535273</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>3810,3925,3870,4355,4135</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="Z109" t="n">
+        <v>32000</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>-17.45</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="n">
+        <v>-11.92</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>947</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>8100</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>592</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>5105</v>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>적자 지속 리스크 및 주가 하락, 악질 종목으로 평가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" t="n">
+        <v>30</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="L110" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>1725000</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>+2.07%</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>1211608</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>2076399149500</v>
+      </c>
+      <c r="R110" t="n">
+        <v>116.86</v>
+      </c>
+      <c r="S110" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="T110" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="U110" t="n">
+        <v>800</v>
+      </c>
+      <c r="V110" t="n">
+        <v>72</v>
+      </c>
+      <c r="W110" t="n">
+        <v>3.268081955072822</v>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>1856000,1853000,1812000,1683000,1712000</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z110" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>40000</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE110" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>-26.43</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>331500</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>12600993</v>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>자사주 매입 및 소각 기대감 속 주가 상승, 반도체 실적 발표 시즌 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:01</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>4</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>한국첨단소재</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>062970</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" t="n">
+        <v>30</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="L111" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="n">
+        <v>3520</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>+4.76%</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>26432021</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>94885944901</v>
+      </c>
+      <c r="R111" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="U111" t="n">
+        <v>80</v>
+      </c>
+      <c r="V111" t="n">
+        <v>2</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0.38630829454736</v>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>1930,1904,1990,2585,3360</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z111" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>68.09</v>
+      </c>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>-952</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>276</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>5100</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>966</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>1060</v>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>양자암호 해독키 독점 공급 및 미국 보안주 상승 수혜, 가벼운 종목으로 빠른 상승 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:01</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>5</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" t="n">
+        <v>30</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="L112" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="n">
+        <v>252000</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>+1.41%</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>4908219</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1226634938250</v>
+      </c>
+      <c r="R112" t="n">
+        <v>166.91</v>
+      </c>
+      <c r="S112" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="T112" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U112" t="n">
+        <v>800</v>
+      </c>
+      <c r="V112" t="n">
+        <v>107</v>
+      </c>
+      <c r="W112" t="n">
+        <v>1.11546029075386</v>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>269500,269000,259500,248500,250500</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z112" t="n">
+        <v>-573000</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>259000</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE112" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>-37.75</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>76700</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>14732622</v>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 반도체 업황 둔화 우려 속, 배당 및 최고점 돌파 기대.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ112"/>
+  <dimension ref="A1:AQ117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16064,10 +16064,8 @@
           <t>10300,9770,9820,10030,10070</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y108" t="n">
+        <v>3</v>
       </c>
       <c r="Z108" t="n">
         <v>-9000</v>
@@ -16209,10 +16207,8 @@
           <t>3810,3925,3870,4355,4135</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
+      <c r="Y109" t="n">
+        <v>-4</v>
       </c>
       <c r="Z109" t="n">
         <v>32000</v>
@@ -16354,10 +16350,8 @@
           <t>1856000,1853000,1812000,1683000,1712000</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y110" t="n">
+        <v>1</v>
       </c>
       <c r="Z110" t="n">
         <v>-12000</v>
@@ -16503,10 +16497,8 @@
           <t>1930,1904,1990,2585,3360</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y111" t="n">
+        <v>4</v>
       </c>
       <c r="Z111" t="n">
         <v>9000</v>
@@ -16648,10 +16640,8 @@
           <t>269500,269000,259500,248500,250500</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y112" t="n">
+        <v>-1</v>
       </c>
       <c r="Z112" t="n">
         <v>-573000</v>
@@ -16707,6 +16697,751 @@
       <c r="AQ112" t="inlineStr">
         <is>
           <t>정치적 이슈와 반도체 업황 둔화 우려 속, 배당 및 최고점 돌파 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>27</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="L113" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="n">
+        <v>31950</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>-1.54%</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>319356</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>10088240750</v>
+      </c>
+      <c r="R113" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="S113" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="T113" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="U113" t="n">
+        <v>230</v>
+      </c>
+      <c r="V113" t="n">
+        <v>2</v>
+      </c>
+      <c r="W113" t="n">
+        <v>1.031994704324801</v>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>31500,31650,31450,30250,32500</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="Z113" t="n">
+        <v>-91000</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="n">
+        <v>-19.05</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>42557</v>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>담관암, 간암 FDA 순차 승인 기대감 있으나, 유럽 신청 시점 및 배경에 대한 의구심 존재. 과거 실패 사례 언급되며 부정적 전망 우세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:01</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>27</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="L114" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="n">
+        <v>3840</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>+29.95%</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>1953233</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>7500409410</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="T114" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="U114" t="n">
+        <v>328</v>
+      </c>
+      <c r="V114" t="n">
+        <v>1</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>2775,2710,2740,3005,4030</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z114" t="n">
+        <v>-29000</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>4588</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>6900</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>1738</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1257</v>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>카카오의 미투온 인수 가능성 제기. 합법 카지노 사업 확장 기대감과 공매도 숏스퀴즈 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:01</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>이뮨온시아</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>424870</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>27</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="L115" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="n">
+        <v>3525</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>5478621</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>20908749761</v>
+      </c>
+      <c r="R115" t="n">
+        <v>74.03</v>
+      </c>
+      <c r="S115" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="T115" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U115" t="n">
+        <v>174</v>
+      </c>
+      <c r="V115" t="n">
+        <v>1</v>
+      </c>
+      <c r="W115" t="n">
+        <v>1.111969111969112</v>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>2880,2845,2755,2900,3515</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="Z115" t="n">
+        <v>-341000</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>-313000</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>16110</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>2300</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>3222</v>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>사기 도박판 및 개미 털기 의혹 제기, 주가 급락 및 2천원대 회귀 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:01</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>27</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="L116" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="n">
+        <v>18600</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>-2.77%</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>3320384</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>62146851285</v>
+      </c>
+      <c r="R116" t="n">
+        <v>61.42</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U116" t="n">
+        <v>125</v>
+      </c>
+      <c r="V116" t="n">
+        <v>17</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0.1152074699680008</v>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>19450,19750,19890,18340,19320</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z116" t="n">
+        <v>-59000</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>-140000</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE116" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>-38.27</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>76429</v>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>주가 조작 의혹 및 대차 해지 운동 참여 독려. 대형 계약 임박 기대감 있으나 구체적 근거 제시 미흡.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:01</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>27</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="L117" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="n">
+        <v>8450</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>-1.86%</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>1860164</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>15779786220</v>
+      </c>
+      <c r="R117" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="S117" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="T117" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U117" t="n">
+        <v>138</v>
+      </c>
+      <c r="V117" t="n">
+        <v>4</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.2493285693731715</v>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>8950,8970,8900,8810,8680</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z117" t="n">
+        <v>-558000</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>-58000</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>-21.15</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE117" t="n">
+        <v>11000</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>-22.45</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>453</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>13208</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>17950</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>8120</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>42250</v>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>LG디스플레이, PBR 0.6배 수준. 개인 주주 손실 누적 및 경영진 성과급 논란.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ117"/>
+  <dimension ref="A1:AQ122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16787,10 +16787,8 @@
           <t>31500,31650,31450,30250,32500</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
+      <c r="Y113" t="n">
+        <v>-1</v>
       </c>
       <c r="Z113" t="n">
         <v>-91000</v>
@@ -16936,10 +16934,8 @@
           <t>2775,2710,2740,3005,4030</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y114" t="n">
+        <v>7</v>
       </c>
       <c r="Z114" t="n">
         <v>-29000</v>
@@ -17085,10 +17081,8 @@
           <t>2880,2845,2755,2900,3515</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
+      <c r="Y115" t="n">
+        <v>-7</v>
       </c>
       <c r="Z115" t="n">
         <v>-341000</v>
@@ -17234,10 +17228,8 @@
           <t>19450,19750,19890,18340,19320</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y116" t="n">
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
         <v>-59000</v>
@@ -17383,10 +17375,8 @@
           <t>8950,8970,8900,8810,8680</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y117" t="n">
+        <v>-6</v>
       </c>
       <c r="Z117" t="n">
         <v>-558000</v>
@@ -17442,6 +17432,751 @@
       <c r="AQ117" t="inlineStr">
         <is>
           <t>LG디스플레이, PBR 0.6배 수준. 개인 주주 손실 누적 및 경영진 성과급 논란.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:01</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>59</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L118" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="n">
+        <v>21500</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>+6.44%</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>2583141</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>54947043125</v>
+      </c>
+      <c r="R118" t="n">
+        <v>293.34</v>
+      </c>
+      <c r="S118" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="T118" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="U118" t="n">
+        <v>91</v>
+      </c>
+      <c r="V118" t="n">
+        <v>4</v>
+      </c>
+      <c r="W118" t="n">
+        <v>4.866566668794281</v>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>21350,21400,22100,20950,20350</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z118" t="n">
+        <v>902000</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>67000</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>281.28</v>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE118" t="n">
+        <v>37000</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>-45.14</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>620</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>4857</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>35350</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>18440</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>189200</v>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>나스닥 반등 및 기관 매수세 유입에 따른 주가 상승 기대감. 60일선 돌파 및 추세 전환 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:01</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>043260</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>59</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L119" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="n">
+        <v>21650</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>+16.65%</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>11885338</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>255968976870</v>
+      </c>
+      <c r="R119" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="S119" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="U119" t="n">
+        <v>81</v>
+      </c>
+      <c r="V119" t="n">
+        <v>1</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3239631208431109</v>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>18560,17480,16830,16950,18880</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z119" t="n">
+        <v>-78000</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>127.87</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>223.13</v>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>1341</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>3536</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>59600</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1030</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>16335</v>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>자회사 ADST의 CPO 생산장비 수주 및 삼성과의 공급 계약 체결. 3분기 영업이익 대폭 상승.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:01</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>59</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L120" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="n">
+        <v>4610</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>+20.05%</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>49102482</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>214988526250</v>
+      </c>
+      <c r="R120" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T120" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U120" t="n">
+        <v>416</v>
+      </c>
+      <c r="V120" t="n">
+        <v>2</v>
+      </c>
+      <c r="W120" t="n">
+        <v>1.156051711852329</v>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>2710,2740,3005,4030,3840</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z120" t="n">
+        <v>-159000</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>4588</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>6900</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1738</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1509</v>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>카카오 및 소프트뱅크 인수설 기반의 텐버거 기대감. 대량 거래 동반한 주가 급등 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:01</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n">
+        <v>59</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L121" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="n">
+        <v>85700</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>+2.27%</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>983424</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>83963354550</v>
+      </c>
+      <c r="R121" t="n">
+        <v>119.98</v>
+      </c>
+      <c r="S121" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="T121" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U121" t="n">
+        <v>160</v>
+      </c>
+      <c r="V121" t="n">
+        <v>17</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1.145661879404013</v>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>89900,90800,85600,86800,84100</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z121" t="n">
+        <v>-71000</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE121" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="n">
+        <v>649.24</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>548961</v>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>FOMC 금리 인상 악재 소멸 후 반등을 기대하며, 대미 원전 투자와 AI 관련 전력 수요 증가를 긍정적 요인으로 분석.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>59</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L122" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="n">
+        <v>253000</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>5058583</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1287071330000</v>
+      </c>
+      <c r="R122" t="n">
+        <v>128.59</v>
+      </c>
+      <c r="S122" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="T122" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="U122" t="n">
+        <v>800</v>
+      </c>
+      <c r="V122" t="n">
+        <v>108</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.5951950058969457</v>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>269000,259500,248500,250500,253500</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z122" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>-55000</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE122" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-36.25</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="inlineStr"/>
+      <c r="AJ122" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>77100</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>14791085</v>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>게시글 대부분이 정치적 논쟁으로 이루어져 주가 관련 분석 부재. 반도체 시장 독점 및 국힘 정권 3년 허송세월 언급.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ122"/>
+  <dimension ref="A1:AQ127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17522,10 +17522,8 @@
           <t>21350,21400,22100,20950,20350</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y118" t="n">
+        <v>3</v>
       </c>
       <c r="Z118" t="n">
         <v>902000</v>
@@ -17671,10 +17669,8 @@
           <t>18560,17480,16830,16950,18880</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y119" t="n">
+        <v>6</v>
       </c>
       <c r="Z119" t="n">
         <v>-78000</v>
@@ -17820,10 +17816,8 @@
           <t>2710,2740,3005,4030,3840</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y120" t="n">
+        <v>7</v>
       </c>
       <c r="Z120" t="n">
         <v>-159000</v>
@@ -17969,10 +17963,8 @@
           <t>89900,90800,85600,86800,84100</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y121" t="n">
+        <v>2</v>
       </c>
       <c r="Z121" t="n">
         <v>-71000</v>
@@ -18118,10 +18110,8 @@
           <t>269000,259500,248500,250500,253500</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y122" t="n">
+        <v>-3</v>
       </c>
       <c r="Z122" t="n">
         <v>-199000</v>
@@ -18177,6 +18167,739 @@
       <c r="AQ122" t="inlineStr">
         <is>
           <t>게시글 대부분이 정치적 논쟁으로 이루어져 주가 관련 분석 부재. 반도체 시장 독점 및 국힘 정권 3년 허송세월 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:01</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>아주IB투자</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>027360</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>53</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L123" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="n">
+        <v>3840</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>+9.71%</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>25603429</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>98406539533</v>
+      </c>
+      <c r="R123" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="S123" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="T123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U123" t="n">
+        <v>160</v>
+      </c>
+      <c r="V123" t="n">
+        <v>1</v>
+      </c>
+      <c r="W123" t="n">
+        <v>1.724279936266699</v>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>3300,3250,3325,3370,3515</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z123" t="n">
+        <v>-382000</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="inlineStr"/>
+      <c r="AJ123" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>69</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>2227</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>19950</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>1913</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>4652</v>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>스페이스X 관련주로 부각되며 상승 시도. 프로그램 매수세 및 기관 순매수 관찰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:01</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>53</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L124" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="n">
+        <v>1742000</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>-0.97%</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>2270739</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>3985651175500</v>
+      </c>
+      <c r="R124" t="n">
+        <v>122.87</v>
+      </c>
+      <c r="S124" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>800</v>
+      </c>
+      <c r="V124" t="n">
+        <v>73</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.2863466414542954</v>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>1853000,1812000,1683000,1712000,1757000</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z124" t="n">
+        <v>-242000</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE124" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>-22.87</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="inlineStr"/>
+      <c r="AJ124" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>333000</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>12725177</v>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>실적 시즌 진입 및 금리 인상 수혜 기대감 속 홀딩 권유. 단기적 등락 가능성 및 투자 주체별 전략 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:01</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>53</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L125" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="n">
+        <v>13720</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>-1.79%</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>1202381</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>16504634800</v>
+      </c>
+      <c r="R125" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U125" t="n">
+        <v>131</v>
+      </c>
+      <c r="V125" t="n">
+        <v>7</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.9773832497105365</v>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>14510,14610,15250,14580,13910</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="Z125" t="n">
+        <v>122000</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="inlineStr"/>
+      <c r="AJ125" t="n">
+        <v>334.63</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>41</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>5307</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>36200</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>8920</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>2058</v>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>유가 변동성 및 지정학적 리스크에 따른 주가 등락. 외국인 매수세와 프로그램 매도 공존.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:01</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>53</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L126" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>8390</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>-0.94%</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>1785560</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>15019976615</v>
+      </c>
+      <c r="R126" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="T126" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="U126" t="n">
+        <v>151</v>
+      </c>
+      <c r="V126" t="n">
+        <v>5</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.1030492904835486</v>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>8970,8900,8810,8680,8510</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z126" t="n">
+        <v>-236000</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>-21.15</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE126" t="n">
+        <v>11000</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>-23.91</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="inlineStr"/>
+      <c r="AJ126" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>453</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>13208</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>17950</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>8120</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>41950</v>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>4분기 전망 및 중국 경쟁 심화 우려. 무능한 경영진과 높은 부채 비중, 목표가 하향 조정 등 악재 지속.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:01</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>008290</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="n">
+        <v>53</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L127" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="n">
+        <v>55</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>-1.79%</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>8738026</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>634666899</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>128</v>
+      </c>
+      <c r="V127" t="n">
+        <v>1</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.1562915341915981</v>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>136,134,99,70,56</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>-13.49</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="inlineStr"/>
+      <c r="AJ127" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>526</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>901</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>방산용 AR 디스플레이 양산 협력 등 신사업 본격화. 차익 실현 및 단기 급등 가능성, 투자 주의 요구.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ127"/>
+  <dimension ref="A1:AQ132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18257,10 +18257,8 @@
           <t>3300,3250,3325,3370,3515</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y123" t="n">
+        <v>4</v>
       </c>
       <c r="Z123" t="n">
         <v>-382000</v>
@@ -18402,10 +18400,8 @@
           <t>1853000,1812000,1683000,1712000,1757000</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y124" t="n">
+        <v>1</v>
       </c>
       <c r="Z124" t="n">
         <v>-242000</v>
@@ -18551,10 +18547,8 @@
           <t>14510,14610,15250,14580,13910</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
+      <c r="Y125" t="n">
+        <v>-3</v>
       </c>
       <c r="Z125" t="n">
         <v>122000</v>
@@ -18696,10 +18690,8 @@
           <t>8970,8900,8810,8680,8510</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y126" t="n">
+        <v>-8</v>
       </c>
       <c r="Z126" t="n">
         <v>-236000</v>
@@ -18845,10 +18837,8 @@
           <t>136,134,99,70,56</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y127" t="n">
+        <v>2</v>
       </c>
       <c r="Z127" t="n">
         <v>0</v>
@@ -18900,6 +18890,751 @@
       <c r="AQ127" t="inlineStr">
         <is>
           <t>방산용 AR 디스플레이 양산 협력 등 신사업 본격화. 차익 실현 및 단기 급등 가능성, 투자 주의 요구.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:01</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>43</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>49</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="n">
+        <v>18800</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>+16.55%</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>34451675</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>614290272570</v>
+      </c>
+      <c r="R128" t="n">
+        <v>125.11</v>
+      </c>
+      <c r="S128" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="T128" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="U128" t="n">
+        <v>296</v>
+      </c>
+      <c r="V128" t="n">
+        <v>18</v>
+      </c>
+      <c r="W128" t="n">
+        <v>11.37312206974436</v>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>14150,14380,14320,16230,16250</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z128" t="n">
+        <v>1514000</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>86000</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="inlineStr"/>
+      <c r="AJ128" t="n">
+        <v>-77.69</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>29231</v>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>수익률 급등 및 2차 매물대 돌파 시도. 외인/기관/투신 매수세 유입 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:01</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>043260</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>43</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>49</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="n">
+        <v>25800</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>+19.44%</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>10216206</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>248592210050</v>
+      </c>
+      <c r="R129" t="n">
+        <v>119</v>
+      </c>
+      <c r="S129" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T129" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="U129" t="n">
+        <v>95</v>
+      </c>
+      <c r="V129" t="n">
+        <v>2</v>
+      </c>
+      <c r="W129" t="n">
+        <v>1.06890892356144</v>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>17480,16830,16950,18880,22200</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z129" t="n">
+        <v>-170000</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>127.87</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>223.13</v>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="inlineStr"/>
+      <c r="AJ129" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1341</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>3536</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>59600</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1030</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>19467</v>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>AI 데이터센터 수혜 및 광통신 관련주 분석. 프로그램/외인 폭풍 매수 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:01</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>43</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>49</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="n">
+        <v>31500</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>+11.31%</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>5495665</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>169715261200</v>
+      </c>
+      <c r="R130" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="S130" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="T130" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U130" t="n">
+        <v>112</v>
+      </c>
+      <c r="V130" t="n">
+        <v>1</v>
+      </c>
+      <c r="W130" t="n">
+        <v>5.346092678914176</v>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>29500,28100,28250,28100,28700</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z130" t="n">
+        <v>253000</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>109.58</v>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE130" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-18.72</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="inlineStr"/>
+      <c r="AJ130" t="n">
+        <v>69.69</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>452</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>8622</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>75900</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>61738</v>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>가온전선과의 비교 속 저평가 해소 기대감. 박스권 상단 돌파 시도.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:01</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>43</v>
+      </c>
+      <c r="I131" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" t="n">
+        <v>49</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="n">
+        <v>19130</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>+3.46%</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>5079012</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>97928708900</v>
+      </c>
+      <c r="R131" t="n">
+        <v>144.74</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="T131" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U131" t="n">
+        <v>113</v>
+      </c>
+      <c r="V131" t="n">
+        <v>19</v>
+      </c>
+      <c r="W131" t="n">
+        <v>1.459796244842974</v>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>19890,18340,19320,18610,18600</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z131" t="n">
+        <v>392000</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>106000</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE131" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>-35.2</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="inlineStr"/>
+      <c r="AJ131" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>78607</v>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>미국장 및 중동 정세 관련 상승 기대감. 대차해지 운동 참여 독려.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:01</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>5</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>43</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>49</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="n">
+        <v>52400</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>+2.54%</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>3476917</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>186679131500</v>
+      </c>
+      <c r="R132" t="n">
+        <v>165.94</v>
+      </c>
+      <c r="S132" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="T132" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U132" t="n">
+        <v>95</v>
+      </c>
+      <c r="V132" t="n">
+        <v>1</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.533331134347066</v>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>51000,50200,51100,50200,51400</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z132" t="n">
+        <v>499000</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>123000</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE132" t="n">
+        <v>61000</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr"/>
+      <c r="AJ132" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>24187</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>67300</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>23150</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>102704</v>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>외인 기관 매수세 확인, 개인 매도세 관찰.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ132"/>
+  <dimension ref="A1:AQ137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18980,10 +18980,8 @@
           <t>14150,14380,14320,16230,16250</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y128" t="n">
+        <v>8</v>
       </c>
       <c r="Z128" t="n">
         <v>1514000</v>
@@ -19129,10 +19127,8 @@
           <t>17480,16830,16950,18880,22200</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y129" t="n">
+        <v>7</v>
       </c>
       <c r="Z129" t="n">
         <v>-170000</v>
@@ -19278,10 +19274,8 @@
           <t>29500,28100,28250,28100,28700</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y130" t="n">
+        <v>2</v>
       </c>
       <c r="Z130" t="n">
         <v>253000</v>
@@ -19427,10 +19421,8 @@
           <t>19890,18340,19320,18610,18600</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y131" t="n">
+        <v>5</v>
       </c>
       <c r="Z131" t="n">
         <v>392000</v>
@@ -19576,10 +19568,8 @@
           <t>51000,50200,51100,50200,51400</t>
         </is>
       </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y132" t="n">
+        <v>4</v>
       </c>
       <c r="Z132" t="n">
         <v>499000</v>
@@ -19635,6 +19625,743 @@
       <c r="AQ132" t="inlineStr">
         <is>
           <t>외인 기관 매수세 확인, 개인 매도세 관찰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>파미셀</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>005690</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" t="n">
+        <v>50</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L133" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="n">
+        <v>12540</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>+8.29%</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>9809981</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>128306456645</v>
+      </c>
+      <c r="R133" t="n">
+        <v>108.92</v>
+      </c>
+      <c r="S133" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="T133" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="U133" t="n">
+        <v>191</v>
+      </c>
+      <c r="V133" t="n">
+        <v>2</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.099285024154589</v>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>11260,10920,10870,11510,11670</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z133" t="n">
+        <v>276000</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>169000</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr"/>
+      <c r="AJ133" t="n">
+        <v>119.43</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>105</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1442</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>21150</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>8140</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>7525</v>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>개인 투자자들의 손실 경험과 외인/기관 동시 매수에 대한 엇갈린 시각.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>50</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L134" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="n">
+        <v>1837000</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>+5.27%</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>2631512</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>4820804257500</v>
+      </c>
+      <c r="R134" t="n">
+        <v>134.58</v>
+      </c>
+      <c r="S134" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="T134" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U134" t="n">
+        <v>800</v>
+      </c>
+      <c r="V134" t="n">
+        <v>74</v>
+      </c>
+      <c r="W134" t="n">
+        <v>5.054859154929577</v>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>1812000,1683000,1712000,1757000,1766000</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z134" t="n">
+        <v>483000</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>116000</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE134" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr"/>
+      <c r="AJ134" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>333000</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>13419145</v>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>200만원 목표 설정, 외인 쌍끌이 매수와 자사주 매입으로 인한 상승 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>50</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L135" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="n">
+        <v>260250</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>+3.07%</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>10572094</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>2749519617500</v>
+      </c>
+      <c r="R135" t="n">
+        <v>152.77</v>
+      </c>
+      <c r="S135" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="U135" t="n">
+        <v>800</v>
+      </c>
+      <c r="V135" t="n">
+        <v>109</v>
+      </c>
+      <c r="W135" t="n">
+        <v>3.062578389901235</v>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>259500,248500,250500,253500,256000</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z135" t="n">
+        <v>-1533000</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>874000</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE135" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-35.25</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr"/>
+      <c r="AJ135" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>78600</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>15214940</v>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>삼성전자 관련 내용은 정치적 논쟁에 치우쳐 투자 분석 정보 부재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>4</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>빛샘전자</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>072950</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>50</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L136" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="n">
+        <v>14120</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>+5.85%</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>13948884</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>209353622685</v>
+      </c>
+      <c r="R136" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="U136" t="n">
+        <v>121</v>
+      </c>
+      <c r="V136" t="n">
+        <v>3</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.232822950638439</v>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>8900,11570,10740,13910,13460</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z136" t="n">
+        <v>-108000</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>37.47</v>
+      </c>
+      <c r="AD136" t="inlineStr"/>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr"/>
+      <c r="AJ136" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>938</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>10357</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>25700</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>4600</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1137</v>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>주가 조작 의혹과 함께 하락 및 조정 가능성 언급, 일부 긍정적 기대감 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-18 15:01</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>5</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>017900</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="n">
+        <v>50</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L137" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="n">
+        <v>10515</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>+2.59%</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>19409294</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>210719873950</v>
+      </c>
+      <c r="R137" t="n">
+        <v>91.31</v>
+      </c>
+      <c r="S137" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="U137" t="n">
+        <v>132</v>
+      </c>
+      <c r="V137" t="n">
+        <v>5</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.2061866541683754</v>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>7900,10270,10720,10590,10200</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z137" t="n">
+        <v>-55000</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr"/>
+      <c r="AJ137" t="n">
+        <v>144.04</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>4784</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>22450</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1760</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>6093</v>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>주가 조작 의혹 제기 및 차익 실현 매도 의견 혼재.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ137"/>
+  <dimension ref="A1:AQ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19715,10 +19715,8 @@
           <t>11260,10920,10870,11510,11670</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="Y133" t="n">
+        <v>-2</v>
       </c>
       <c r="Z133" t="n">
         <v>276000</v>
@@ -19864,10 +19862,8 @@
           <t>1812000,1683000,1712000,1757000,1766000</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y134" t="n">
+        <v>3</v>
       </c>
       <c r="Z134" t="n">
         <v>483000</v>
@@ -20013,10 +20009,8 @@
           <t>259500,248500,250500,253500,256000</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y135" t="n">
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
         <v>-1533000</v>
@@ -20162,10 +20156,8 @@
           <t>8900,11570,10740,13910,13460</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="Y136" t="n">
+        <v>-2</v>
       </c>
       <c r="Z136" t="n">
         <v>-108000</v>
@@ -20307,10 +20299,8 @@
           <t>7900,10270,10720,10590,10200</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y137" t="n">
+        <v>0</v>
       </c>
       <c r="Z137" t="n">
         <v>-55000</v>
@@ -20362,6 +20352,743 @@
       <c r="AQ137" t="inlineStr">
         <is>
           <t>주가 조작 의혹 제기 및 차익 실현 매도 의견 혼재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:01</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>49</v>
+      </c>
+      <c r="K138" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L138" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="n">
+        <v>272750</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>+4.50%</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>11797499</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>3189758272500</v>
+      </c>
+      <c r="R138" t="n">
+        <v>179.59</v>
+      </c>
+      <c r="S138" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="T138" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U138" t="n">
+        <v>800</v>
+      </c>
+      <c r="V138" t="n">
+        <v>110</v>
+      </c>
+      <c r="W138" t="n">
+        <v>3.969597988693901</v>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>248500,250500,253500,256000,260000</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z138" t="n">
+        <v>3622000</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>391000</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE138" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-32.5</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="inlineStr"/>
+      <c r="AJ138" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>81100</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>15945725</v>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>신한증권 시스템 오류 발생 속, 27만원 목표주가 및 3분기 실적 발표, 자사주 소각/배당 관련 언급. 10월 이후 상승 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:01</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>49</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L139" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="n">
+        <v>25250</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>+29.89%</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>8832375</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>203172135535</v>
+      </c>
+      <c r="R139" t="n">
+        <v>103.82</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T139" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="U139" t="n">
+        <v>188</v>
+      </c>
+      <c r="V139" t="n">
+        <v>1</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>23450,20850,20800,20200,19540</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z139" t="n">
+        <v>114000</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr"/>
+      <c r="AJ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>39350</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>4737</v>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>미국 타임지 선정 '세계 최고 헬스테크 기업' 선정 소식에 따른 급등. 2주간의 급락 이후 상승 전환하며 전고점 돌파 기대감 형성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:01</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" t="n">
+        <v>49</v>
+      </c>
+      <c r="K140" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="n">
+        <v>31550</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>+6.41%</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>808913</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>25413173625</v>
+      </c>
+      <c r="R140" t="n">
+        <v>107.31</v>
+      </c>
+      <c r="S140" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="T140" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="U140" t="n">
+        <v>361</v>
+      </c>
+      <c r="V140" t="n">
+        <v>1</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1.573800401386608</v>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>30250,32500,31750,31800,30050</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z140" t="n">
+        <v>-148000</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="inlineStr"/>
+      <c r="AJ140" t="n">
+        <v>-18.81</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>42024</v>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>FDA 신약 승인 과정에서 제품명 조건부 수용 관련 내용, 리보세라닙 동일시 우려. 투자자 손실 관련 경고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:01</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>4</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>272210</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" t="n">
+        <v>49</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="n">
+        <v>78500</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>-1.88%</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>1155069</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>90521060450</v>
+      </c>
+      <c r="R141" t="n">
+        <v>176.31</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="T141" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U141" t="n">
+        <v>146</v>
+      </c>
+      <c r="V141" t="n">
+        <v>1</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1.184123076923077</v>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>73300,70200,68900,79600,79900</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z141" t="n">
+        <v>-499000</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>-56000</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>159.15</v>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE141" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>-12.33</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr"/>
+      <c r="AJ141" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1282</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>25933</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>184000</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>44750</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>148302</v>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>유럽 K-방산 드론 시장 진출 관련 뉴스 언급. 공매도 금지 및 10만원대 상승 기대와 함께, 8만원 돌파 시 추가 상승 가능성 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:01</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>5</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>017900</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>49</v>
+      </c>
+      <c r="K142" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L142" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="n">
+        <v>11080</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>+5.32%</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>14555479</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>168865612600</v>
+      </c>
+      <c r="R142" t="n">
+        <v>82.87</v>
+      </c>
+      <c r="S142" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U142" t="n">
+        <v>96</v>
+      </c>
+      <c r="V142" t="n">
+        <v>6</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.067935601554445</v>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>10270,10720,10590,10200,10560</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z142" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr"/>
+      <c r="AJ142" t="n">
+        <v>151.78</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>4784</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>22450</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1760</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>6420</v>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>미국 광통신주 급등 및 나스닥 선물 상승에 따른 재진입 언급. 20% 상승 기대와 더불어, 단기 고점 및 하락 가능성도 함께 제시.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ142"/>
+  <dimension ref="A1:AQ147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20442,10 +20442,8 @@
           <t>248500,250500,253500,256000,260000</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y138" t="n">
+        <v>2</v>
       </c>
       <c r="Z138" t="n">
         <v>3622000</v>
@@ -20591,10 +20589,8 @@
           <t>23450,20850,20800,20200,19540</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y139" t="n">
+        <v>7</v>
       </c>
       <c r="Z139" t="n">
         <v>114000</v>
@@ -20736,10 +20732,8 @@
           <t>30250,32500,31750,31800,30050</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y140" t="n">
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
         <v>-148000</v>
@@ -20885,10 +20879,8 @@
           <t>73300,70200,68900,79600,79900</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y141" t="n">
+        <v>4</v>
       </c>
       <c r="Z141" t="n">
         <v>-499000</v>
@@ -21034,10 +21026,8 @@
           <t>10270,10720,10590,10200,10560</t>
         </is>
       </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y142" t="n">
+        <v>3</v>
       </c>
       <c r="Z142" t="n">
         <v>-6000</v>
@@ -21089,6 +21079,751 @@
       <c r="AQ142" t="inlineStr">
         <is>
           <t>미국 광통신주 급등 및 나스닥 선물 상승에 따른 재진입 언급. 20% 상승 기대와 더불어, 단기 고점 및 하락 가능성도 함께 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:01</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>950260</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>39</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="L143" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="n">
+        <v>20800</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>+12.62%</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>6181369</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>127293116845</v>
+      </c>
+      <c r="R143" t="n">
+        <v>101.83</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="U143" t="n">
+        <v>161</v>
+      </c>
+      <c r="V143" t="n">
+        <v>2</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.9860252161137117</v>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>14140,15130,15360,17520,18330</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z143" t="n">
+        <v>17000</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>48000</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE143" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="inlineStr"/>
+      <c r="AJ143" t="n">
+        <v>-33.44</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>46.85</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>-622</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>444</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>21950</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>9900</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>10284</v>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>혈관 치료 기술 확장 및 글로벌 임상 3상 진입 소식. MSD의 EyeBio 인수 사례 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:01</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>39</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="L144" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="n">
+        <v>1866000</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>+0.48%</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>2256970</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>4222681976000</v>
+      </c>
+      <c r="R144" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="S144" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="U144" t="n">
+        <v>800</v>
+      </c>
+      <c r="V144" t="n">
+        <v>75</v>
+      </c>
+      <c r="W144" t="n">
+        <v>1.265055674010898</v>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>1683000,1712000,1757000,1766000,1849000</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z144" t="n">
+        <v>-87000</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE144" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>-18.48</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="inlineStr"/>
+      <c r="AJ144" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>333000</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>13630988</v>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>신한증권 앱 오류 관련 불만 속에서 주가 반등 기대감. 반도체 수출 지표 및 2시 이후 반등 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:01</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>39</v>
+      </c>
+      <c r="K145" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="L145" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="n">
+        <v>18290</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>-3.28%</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>4543863</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>83658568300</v>
+      </c>
+      <c r="R145" t="n">
+        <v>60.01</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>122</v>
+      </c>
+      <c r="V145" t="n">
+        <v>20</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0.1531950115881249</v>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>18340,19320,18610,18600,19020</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="Z145" t="n">
+        <v>-699000</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>-239000</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE145" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="inlineStr"/>
+      <c r="AJ145" t="n">
+        <v>-8.33</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>75155</v>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>공매도 관련 불만 및 대차 해지 운동 촉구. 주가 상승 저지 세력 존재 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>4</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>475830</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>39</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="L146" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="n">
+        <v>27000</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>-27.81%</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>4425327</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>120659134075</v>
+      </c>
+      <c r="R146" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="S146" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U146" t="n">
+        <v>800</v>
+      </c>
+      <c r="V146" t="n">
+        <v>1</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0.4777368306958595</v>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>49200,50200,50800,35500,37400</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="Z146" t="n">
+        <v>135000</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>56.98</v>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr"/>
+      <c r="AJ146" t="n">
+        <v>-13.39</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>-2016</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>6165</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>146600</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>26200</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>5873</v>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>급락에 대한 불만 및 주가 조작 의혹 제기. 추가 하락 가능성 및 매수 금지 의견.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:01</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>5</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>000500</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>39</v>
+      </c>
+      <c r="K147" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="L147" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="n">
+        <v>317000</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>-3.06%</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>299472</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>95740768750</v>
+      </c>
+      <c r="R147" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="S147" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U147" t="n">
+        <v>133</v>
+      </c>
+      <c r="V147" t="n">
+        <v>1</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.035559986706547</v>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>236000,246000,247000,264000,322000</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z147" t="n">
+        <v>-66000</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>213.29</v>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE147" t="n">
+        <v>290000</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr"/>
+      <c r="AJ147" t="n">
+        <v>177.39</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1787</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>16247</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>635000</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>52600</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>94395</v>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>52주 신고가 돌파 및 기관 목표가 상향 기대감. 외국인 재유입 신호 감지.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ147"/>
+  <dimension ref="A1:AQ152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21169,10 +21169,8 @@
           <t>14140,15130,15360,17520,18330</t>
         </is>
       </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y143" t="n">
+        <v>2</v>
       </c>
       <c r="Z143" t="n">
         <v>17000</v>
@@ -21318,10 +21316,8 @@
           <t>1683000,1712000,1757000,1766000,1849000</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y144" t="n">
+        <v>1</v>
       </c>
       <c r="Z144" t="n">
         <v>-87000</v>
@@ -21467,10 +21463,8 @@
           <t>18340,19320,18610,18600,19020</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
+      <c r="Y145" t="n">
+        <v>-2</v>
       </c>
       <c r="Z145" t="n">
         <v>-699000</v>
@@ -21616,10 +21610,8 @@
           <t>49200,50200,50800,35500,37400</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
+      <c r="Y146" t="n">
+        <v>-8</v>
       </c>
       <c r="Z146" t="n">
         <v>135000</v>
@@ -21765,10 +21757,8 @@
           <t>236000,246000,247000,264000,322000</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y147" t="n">
+        <v>3</v>
       </c>
       <c r="Z147" t="n">
         <v>-66000</v>
@@ -21824,6 +21814,747 @@
       <c r="AQ147" t="inlineStr">
         <is>
           <t>52주 신고가 돌파 및 기관 목표가 상향 기대감. 외국인 재유입 신호 감지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>삼미금속</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>012210</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>60</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L148" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="n">
+        <v>13390</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>+20.41%</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>10641778</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>136300367030</v>
+      </c>
+      <c r="R148" t="n">
+        <v>104.92</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="T148" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="U148" t="n">
+        <v>105</v>
+      </c>
+      <c r="V148" t="n">
+        <v>1</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0.6969884256658051</v>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>11600,10860,11410,11160,11070</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z148" t="n">
+        <v>17000</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr"/>
+      <c r="AJ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>20850</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>4020</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>3087</v>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>대미 투자 1호 텍사스 가스발전 사업 확정으로 인한 가스터빈 관련주 부각. 주가 급등세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" t="n">
+        <v>60</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L149" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="n">
+        <v>32150</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>+8.25%</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>7041536</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>227775347225</v>
+      </c>
+      <c r="R149" t="n">
+        <v>108.04</v>
+      </c>
+      <c r="S149" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="T149" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="U149" t="n">
+        <v>97</v>
+      </c>
+      <c r="V149" t="n">
+        <v>3</v>
+      </c>
+      <c r="W149" t="n">
+        <v>2.503815420056152</v>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>28250,28100,28700,31650,30250</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z149" t="n">
+        <v>262000</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>109.58</v>
+      </c>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="inlineStr"/>
+      <c r="AJ149" t="n">
+        <v>71.13</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>452</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>8622</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>75900</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>63012</v>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>단기 35,000원 목표 제시. AI 전력 수요 폭증 관련 수혜 기대감 있으나, 경쟁 종목 대비 부진.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>3</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>코리아써키트</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>007810</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>60</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L150" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="n">
+        <v>65900</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>+26.00%</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>2240817</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>147285556500</v>
+      </c>
+      <c r="R150" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="S150" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="T150" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U150" t="n">
+        <v>99</v>
+      </c>
+      <c r="V150" t="n">
+        <v>1</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0.1687954005577168</v>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>50100,50600,52300,52200,52900</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z150" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>49000</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>81.62</v>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE150" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>-27.67</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="inlineStr"/>
+      <c r="AJ150" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1726</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>16070</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>148300</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>16300</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>15805</v>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>반도체 업황 개선 및 키맞추기 장세 속 급등. 20일선 안착 여부가 중요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>4</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>60</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L151" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="n">
+        <v>281000</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>+2.55%</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>7533779</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>2114268661000</v>
+      </c>
+      <c r="R151" t="n">
+        <v>131.61</v>
+      </c>
+      <c r="S151" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U151" t="n">
+        <v>800</v>
+      </c>
+      <c r="V151" t="n">
+        <v>111</v>
+      </c>
+      <c r="W151" t="n">
+        <v>2.830970357392582</v>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>250500,253500,256000,260000,275000</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z151" t="n">
+        <v>-116000</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>128000</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE151" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>-29.69</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr"/>
+      <c r="AJ151" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>81100</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>16428043</v>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>AI 낙관론 및 배당 기대감 속 주가 상승 전망. HBM 1위 기업으로서 목표가 56만원 제시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" t="n">
+        <v>60</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L152" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="n">
+        <v>1920000</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>+2.78%</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>1335504</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>2566222055000</v>
+      </c>
+      <c r="R152" t="n">
+        <v>101.57</v>
+      </c>
+      <c r="S152" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="T152" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U152" t="n">
+        <v>800</v>
+      </c>
+      <c r="V152" t="n">
+        <v>76</v>
+      </c>
+      <c r="W152" t="n">
+        <v>2.951304030640161</v>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>1712000,1757000,1766000,1849000,1879000</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z152" t="n">
+        <v>82000</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE152" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>-16.61</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="inlineStr"/>
+      <c r="AJ152" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>333000</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>14025453</v>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>AI 주 강세 및 미국 반도체주 폭등에 따른 동반 상승 기대. 230-240까지 상승 전망.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ152"/>
+  <dimension ref="A1:AQ157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21904,10 +21904,8 @@
           <t>11600,10860,11410,11160,11070</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y148" t="n">
+        <v>8</v>
       </c>
       <c r="Z148" t="n">
         <v>17000</v>
@@ -22053,10 +22051,8 @@
           <t>28250,28100,28700,31650,30250</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y149" t="n">
+        <v>1</v>
       </c>
       <c r="Z149" t="n">
         <v>262000</v>
@@ -22198,10 +22194,8 @@
           <t>50100,50600,52300,52200,52900</t>
         </is>
       </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y150" t="n">
+        <v>3</v>
       </c>
       <c r="Z150" t="n">
         <v>-2000</v>
@@ -22347,10 +22341,8 @@
           <t>250500,253500,256000,260000,275000</t>
         </is>
       </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y151" t="n">
+        <v>3</v>
       </c>
       <c r="Z151" t="n">
         <v>-116000</v>
@@ -22496,10 +22488,8 @@
           <t>1712000,1757000,1766000,1849000,1879000</t>
         </is>
       </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y152" t="n">
+        <v>6</v>
       </c>
       <c r="Z152" t="n">
         <v>82000</v>
@@ -22555,6 +22545,751 @@
       <c r="AQ152" t="inlineStr">
         <is>
           <t>AI 주 강세 및 미국 반도체주 폭등에 따른 동반 상승 기대. 230-240까지 상승 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:01</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" t="n">
+        <v>46</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="n">
+        <v>86600</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>+1.52%</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>2673426</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>231255781550</v>
+      </c>
+      <c r="R153" t="n">
+        <v>122.11</v>
+      </c>
+      <c r="S153" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="T153" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="U153" t="n">
+        <v>431</v>
+      </c>
+      <c r="V153" t="n">
+        <v>19</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0.8393823764309166</v>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>86800,84100,86400,85700,86500</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z153" t="n">
+        <v>-253000</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>136.43</v>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE153" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr"/>
+      <c r="AJ153" t="n">
+        <v>656.0599999999999</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>12156</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>139200</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>57000</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>554726</v>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>대미 투자(SMR, 가스터빈) 관련 공급 계약 체결 및 사업 추진 확정. 긍정적 뉴스에 힘입어 주가 상승 기대감이 매우 높으며, 공매도 세력에 대한 비판 의견도 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:01</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>노타</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>486990</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>46</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="n">
+        <v>22550</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>+29.97%</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>2445096</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>52591170040</v>
+      </c>
+      <c r="R154" t="n">
+        <v>82.17</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U154" t="n">
+        <v>145</v>
+      </c>
+      <c r="V154" t="n">
+        <v>1</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>16960,16830,17310,17460,17490</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z154" t="n">
+        <v>170000</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>-132.79</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="inlineStr"/>
+      <c r="AJ154" t="n">
+        <v>-23.06</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>-978</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1288</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>65300</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>15130</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>4824</v>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 소식과 함께 기술력에 대한 높은 평가. 퓨리오사 AI 관련주로 부각되며, 로봇팔 작업 속도 초가속 등 혁신적인 기술력으로 큰 폭의 상승이 전망됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:01</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>950260</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" t="n">
+        <v>46</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="n">
+        <v>23400</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>+8.84%</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>4486980</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>100084507600</v>
+      </c>
+      <c r="R155" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T155" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U155" t="n">
+        <v>120</v>
+      </c>
+      <c r="V155" t="n">
+        <v>3</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0.6984817692767483</v>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>15130,15360,17520,18330,21850</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z155" t="n">
+        <v>-43000</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE155" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="inlineStr"/>
+      <c r="AJ155" t="n">
+        <v>-37.62</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>-622</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>444</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>24100</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>9900</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>11570</v>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>모더나, 머크 등 글로벌 제약사들의 임상 투자 소식과 함께 주가 상승 기대감이 높음. 기타법인 및 외국인의 매수세 유입으로 신고가 돌파 및 향후 3만 원 돌파 가능성에 대한 전망이 나옴.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:01</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>4</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>46</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="n">
+        <v>18890</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>+3.28%</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>8426758</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>159967900870</v>
+      </c>
+      <c r="R156" t="n">
+        <v>107.83</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="T156" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="U156" t="n">
+        <v>156</v>
+      </c>
+      <c r="V156" t="n">
+        <v>21</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0.7310088459023164</v>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>19320,18610,18600,19020,18480</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z156" t="n">
+        <v>388000</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>96000</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>-14.26</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE156" t="n">
+        <v>24000</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>-22.06</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="inlineStr"/>
+      <c r="AJ156" t="n">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>-2195</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>8148</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>40350</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>77620</v>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>공매도 세력과의 싸움 속에서 2만 돌파 및 상한가 기대감 형성. 감사원 신고 완료 및 공매도 장부 조작 의혹 제기.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-22 15:01</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>5</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>000500</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" t="n">
+        <v>46</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="n">
+        <v>322500</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>+1.26%</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>390062</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>130209786750</v>
+      </c>
+      <c r="R157" t="n">
+        <v>82.19</v>
+      </c>
+      <c r="S157" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T157" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="U157" t="n">
+        <v>141</v>
+      </c>
+      <c r="V157" t="n">
+        <v>2</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.366203703703704</v>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>246000,247000,264000,322000,326000</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z157" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>213.29</v>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE157" t="n">
+        <v>290000</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="inlineStr"/>
+      <c r="AJ157" t="n">
+        <v>180.47</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1787</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>16247</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>635000</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>52600</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>96033</v>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>52주 신고가 돌파 및 40만원, 50만원 목표 제시. 구리 가격 상승 및 발전 프로젝트 테마 언급. 야수의 심장으로 덤빌 구간 진입.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ157"/>
+  <dimension ref="A1:AQ162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22635,10 +22635,8 @@
           <t>86800,84100,86400,85700,86500</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Y153" t="n">
+        <v>8</v>
       </c>
       <c r="Z153" t="n">
         <v>-253000</v>
@@ -22784,10 +22782,8 @@
           <t>16960,16830,17310,17460,17490</t>
         </is>
       </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Y154" t="n">
+        <v>9</v>
       </c>
       <c r="Z154" t="n">
         <v>170000</v>
@@ -22933,10 +22929,8 @@
           <t>15130,15360,17520,18330,21850</t>
         </is>
       </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Y155" t="n">
+        <v>6</v>
       </c>
       <c r="Z155" t="n">
         <v>-43000</v>
@@ -23082,10 +23076,8 @@
           <t>19320,18610,18600,19020,18480</t>
         </is>
       </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y156" t="n">
+        <v>5</v>
       </c>
       <c r="Z156" t="n">
         <v>388000</v>
@@ -23231,10 +23223,8 @@
           <t>246000,247000,264000,322000,326000</t>
         </is>
       </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y157" t="n">
+        <v>5</v>
       </c>
       <c r="Z157" t="n">
         <v>-8000</v>
@@ -23290,6 +23280,747 @@
       <c r="AQ157" t="inlineStr">
         <is>
           <t>52주 신고가 돌파 및 40만원, 50만원 목표 제시. 구리 가격 상승 및 발전 프로젝트 테마 언급. 야수의 심장으로 덤빌 구간 진입.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>레메디</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>387690</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>24</v>
+      </c>
+      <c r="K158" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="L158" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="n">
+        <v>18800</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>+21.13%</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>4184470</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>76210988025</v>
+      </c>
+      <c r="R158" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="S158" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T158" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U158" t="n">
+        <v>127</v>
+      </c>
+      <c r="V158" t="n">
+        <v>1</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0.3338249754178958</v>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>15820,15820,15660,17150,15430</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z158" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="inlineStr"/>
+      <c r="AJ158" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>777</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1729</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>34650</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>6980</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1434</v>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>NASA 선정 및 스페이스X 협력에 따른 초소형 X-ray 기술력 검증. 인도발 수주 재료와 함께 시총 1조 기대감 고조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:01</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>엑스게이트</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>356680</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" t="n">
+        <v>24</v>
+      </c>
+      <c r="K159" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="L159" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="n">
+        <v>18710</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>+13.12%</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>14261017</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>272504636590</v>
+      </c>
+      <c r="R159" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="S159" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="T159" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="U159" t="n">
+        <v>138</v>
+      </c>
+      <c r="V159" t="n">
+        <v>1</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0.2161925725251157</v>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>17120,17700,17360,18040,16740</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z159" t="n">
+        <v>-46000</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="inlineStr"/>
+      <c r="AJ159" t="n">
+        <v>133.64</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1557</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>30550</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>6100</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>5340</v>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>미국 양자 관련주 급등에 따른 기대감. 아이온큐 급등 및 양자 보안 관련 장비 언급. 공매도 세력에 대한 경계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:01</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>24</v>
+      </c>
+      <c r="K160" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="L160" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="n">
+        <v>283000</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>+2.35%</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>9262500</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>2626013033500</v>
+      </c>
+      <c r="R160" t="n">
+        <v>131.47</v>
+      </c>
+      <c r="S160" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="T160" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="U160" t="n">
+        <v>800</v>
+      </c>
+      <c r="V160" t="n">
+        <v>112</v>
+      </c>
+      <c r="W160" t="n">
+        <v>2.854317718235679</v>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>253500,256000,260000,275000,277500</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z160" t="n">
+        <v>1744000</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>499000</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>31.39</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>매수</t>
+        </is>
+      </c>
+      <c r="AE160" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI160" t="inlineStr"/>
+      <c r="AJ160" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>6564</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>63997</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>374500</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>82400</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>16544968</v>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>대통령 및 정당 관련 정치적 언급과 함께 주가 상승 및 보유를 독려하는 의견이 혼재함. 단기적 주가 상승 기대 및 보유 의견이 있으나, 명확한 팩트 기반 근거는 부족함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>4</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LG디스플레이</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>24</v>
+      </c>
+      <c r="K161" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="L161" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>8480</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>2281785</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>19804574575</v>
+      </c>
+      <c r="R161" t="n">
+        <v>94.47</v>
+      </c>
+      <c r="S161" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U161" t="n">
+        <v>91</v>
+      </c>
+      <c r="V161" t="n">
+        <v>8</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0.05478610521612867</v>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>8510,8440,8420,8570,8520</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z161" t="n">
+        <v>353000</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>-21.15</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE161" t="n">
+        <v>11500</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>-24.35</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" t="inlineStr"/>
+      <c r="AJ161" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>453</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>13208</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>17950</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>8120</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>42400</v>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>유리 기판 사업 경쟁력 강화와 실적 개선 전망. 목표 주가 하향 리포트에 대한 불신 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>5</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>24</v>
+      </c>
+      <c r="K162" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="L162" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="n">
+        <v>3860</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>+3.62%</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>15346999</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>61111104381</v>
+      </c>
+      <c r="R162" t="n">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="T162" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="U162" t="n">
+        <v>112</v>
+      </c>
+      <c r="V162" t="n">
+        <v>6</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0.4347942187656464</v>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>3840,4550,4175,4080,3750</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="Z162" t="n">
+        <v>-41000</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="inlineStr"/>
+      <c r="AJ162" t="n">
+        <v>154.4</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>4588</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>6300</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1738</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1263</v>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>급격한 주가 하락 및 물량 떠넘기기 의혹 제기. 단기 단타장으로 변질된 시장에 대한 불만.</t>
         </is>
       </c>
     </row>

--- a/data/reports/monthly_research_2026-09.xlsx
+++ b/data/reports/monthly_research_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ162"/>
+  <dimension ref="A1:AQ167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23370,10 +23370,8 @@
           <t>15820,15820,15660,17150,15430</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Y158" t="n">
+        <v>9</v>
       </c>
       <c r="Z158" t="n">
         <v>2000</v>
@@ -23515,10 +23513,8 @@
           <t>17120,17700,17360,18040,16740</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y159" t="n">
+        <v>7</v>
       </c>
       <c r="Z159" t="n">
         <v>-46000</v>
@@ -23664,10 +23660,8 @@
           <t>253500,256000,260000,275000,277500</t>
         </is>
       </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y160" t="n">
+        <v>1</v>
       </c>
       <c r="Z160" t="n">
         <v>1744000</v>
@@ -23813,10 +23807,8 @@
           <t>8510,8440,8420,8570,8520</t>
         </is>
       </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y161" t="n">
+        <v>1</v>
       </c>
       <c r="Z161" t="n">
         <v>353000</v>
@@ -23962,10 +23954,8 @@
           <t>3840,4550,4175,4080,3750</t>
         </is>
       </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
+      <c r="Y162" t="n">
+        <v>-6</v>
       </c>
       <c r="Z162" t="n">
         <v>-41000</v>
@@ -24021,6 +24011,747 @@
       <c r="AQ162" t="inlineStr">
         <is>
           <t>급격한 주가 하락 및 물량 떠넘기기 의혹 제기. 단기 단타장으로 변질된 시장에 대한 불만.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:01</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>나라스페이스테크놀로지</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>478340</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="I163" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" t="n">
+        <v>24</v>
+      </c>
+      <c r="K163" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="L163" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="n">
+        <v>14080</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>+8.06%</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>8595442</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>129367754790</v>
+      </c>
+      <c r="R163" t="n">
+        <v>79.69</v>
+      </c>
+      <c r="S163" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T163" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="U163" t="n">
+        <v>142</v>
+      </c>
+      <c r="V163" t="n">
+        <v>1</v>
+      </c>
+      <c r="W163" t="n">
+        <v>2.244296852440081</v>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>10700,13850,14100,14210,12820</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="Z163" t="n">
+        <v>-11000</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>-125000</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="inlineStr"/>
+      <c r="AJ163" t="n">
+        <v>-11.79</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>-1194</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>-4583</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>64600</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>7520</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1635</v>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>초소형위성 테마 관련 국방과제 주관 뉴스 및 67억원 규모 계약 내용이 있으나, 투기 과열 및 단일가 지정 관련 우려와 함께 주가 급락에 대한 불만 표출.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:01</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>2</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>우리로</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>046970</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>24</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="L164" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="n">
+        <v>7920</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>+4.07%</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>11207489</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>91751965510</v>
+      </c>
+      <c r="R164" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="S164" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T164" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="U164" t="n">
+        <v>121</v>
+      </c>
+      <c r="V164" t="n">
+        <v>1</v>
+      </c>
+      <c r="W164" t="n">
+        <v>0.288666189453591</v>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>7280,7120,8140,8000,7710</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z164" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr"/>
+      <c r="AJ164" t="n">
+        <v>-440</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>903</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>16200</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>1206</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>3471</v>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>양자 보안 테마 관련 언급 및 기대감이 있으나, 주가 계단식 하락 및 매물대 돌파 여부에 대한 불확실성 존재. 외인 매도세 정리 후 상승 가능성 언급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:01</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>24</v>
+      </c>
+      <c r="K165" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="L165" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="n">
+        <v>1852000</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>+0.65%</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>2499428</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>4646149567500</v>
+      </c>
+      <c r="R165" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="S165" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="T165" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U165" t="n">
+        <v>800</v>
+      </c>
+      <c r="V165" t="n">
+        <v>77</v>
+      </c>
+      <c r="W165" t="n">
+        <v>0.8616461545500297</v>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>1757000,1766000,1849000,1879000,1841000</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="Z165" t="n">
+        <v>-536000</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>91000</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AE165" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="inlineStr"/>
+      <c r="AJ165" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>58955</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>171751</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>333000</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>13528719</v>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>환율 및 국장 전체에 대한 부정적 언급과 함께, 주가 하락에 대한 불만 및 사기 의혹 제기. 자사주 매입 외에는 상승 어렵다는 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:01</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>4</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" t="n">
+        <v>24</v>
+      </c>
+      <c r="K166" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="L166" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="n">
+        <v>30550</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>-1.61%</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>451557</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>13873132750</v>
+      </c>
+      <c r="R166" t="n">
+        <v>88.72</v>
+      </c>
+      <c r="S166" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U166" t="n">
+        <v>377</v>
+      </c>
+      <c r="V166" t="n">
+        <v>2</v>
+      </c>
+      <c r="W166" t="n">
+        <v>0.2171926364234057</v>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>31750,31800,30050,31900,31150</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z166" t="n">
+        <v>-122000</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>-54.43</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>114.94</v>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="inlineStr"/>
+      <c r="AJ166" t="n">
+        <v>-18.22</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>3159</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>69200</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>24150</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>40692</v>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>미국 릴리사 항암제 관련 긍정적인 소식과 함께 승인 기대감이 높으나, 실제 결과 발표 지연.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>5</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>24</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="L167" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="n">
+        <v>17730</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>8101235</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>144151404830</v>
+      </c>
+      <c r="R167" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="S167" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="T167" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="U167" t="n">
+        <v>150</v>
+      </c>
+      <c r="V167" t="n">
+        <v>21</v>
+      </c>
+      <c r="W167" t="n">
+        <v>0.6566775244299674</v>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>16230,16250,18400,18060,17850</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z167" t="n">
+        <v>-273000</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>155.22</v>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>NotRated</t>
+        </is>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="inlineStr"/>
+      <c r="AJ167" t="n">
+        <v>-73.26000000000001</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>-242</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>31500</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>27568</v>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>명절 전 상승 기대감 속 2만원 돌파 시도 및 주포 활동 언급. 단타 세력의 빠른 이탈 촉구.</t>
         </is>
       </c>
     </row>
